--- a/public/exports/29189633.xlsx
+++ b/public/exports/29189633.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366596</t>
+          <t xml:space="preserve">311366598</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366589</t>
+          <t xml:space="preserve">311366590</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379031</t>
+          <t xml:space="preserve">311379034</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379054</t>
+          <t xml:space="preserve">311379055</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381685</t>
+          <t xml:space="preserve">311381687</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">

--- a/public/exports/29189633.xlsx
+++ b/public/exports/29189633.xlsx
@@ -3064,7 +3064,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366598</t>
+          <t xml:space="preserve">311366599</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366590</t>
+          <t xml:space="preserve">311366591</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379064</t>
+          <t xml:space="preserve">311379069</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379047</t>
+          <t xml:space="preserve">311379050</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379055</t>
+          <t xml:space="preserve">311379059</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381687</t>
+          <t xml:space="preserve">311381685</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422167</t>
+          <t xml:space="preserve">311422168</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">

--- a/public/exports/29189633.xlsx
+++ b/public/exports/29189633.xlsx
@@ -3139,7 +3139,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366591</t>
+          <t xml:space="preserve">311366589</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422168</t>
+          <t xml:space="preserve">311422167</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
